--- a/public/exports-60-250/32264328.xlsx
+++ b/public/exports-60-250/32264328.xlsx
@@ -2314,7 +2314,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929294</t>
+          <t xml:space="preserve">311929675</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
